--- a/dataset/bd_pagamentos.xlsx
+++ b/dataset/bd_pagamentos.xlsx
@@ -740,7 +740,7 @@
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>LEG-3E4F5F35</t>
+          <t>PAG-EE2A7BAC</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>LEG-3E4F5F35</t>
+          <t>PAG-EE2A7BAC</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -864,7 +864,7 @@
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>LEG-3E4F5F35</t>
+          <t>PAG-EE2A7BAC</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -926,7 +926,7 @@
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>LEG-3E4F5F35</t>
+          <t>PAG-EE2A7BAC</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
